--- a/diseases/d139/2010-2014.xlsx
+++ b/diseases/d139/2010-2014.xlsx
@@ -774,11 +774,6 @@
       <c r="R2" t="n">
         <v>2.156677078880562</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -796,12 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -811,11 +801,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -939,11 +924,6 @@
       <c r="R3" t="n">
         <v>1.399221446609716</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -961,12 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -976,11 +951,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1104,11 +1074,6 @@
       <c r="R4" t="n">
         <v>1.243665542768747</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1126,12 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1141,11 +1101,6 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1269,11 +1224,6 @@
       <c r="R5" t="n">
         <v>0.9005045287678169</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1291,12 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1306,11 +1251,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1434,11 +1374,6 @@
       <c r="R6" t="n">
         <v>0.5526533870128878</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1456,12 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1471,11 +1401,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1599,11 +1524,6 @@
       <c r="R7" t="n">
         <v>0.3580130852219273</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1621,12 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1636,11 +1551,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1764,11 +1674,6 @@
       <c r="R8" t="n">
         <v>0.3189286872719352</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1786,12 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1801,11 +1701,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1929,11 +1824,6 @@
       <c r="R9" t="n">
         <v>0.2493584589209493</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -1951,12 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1966,11 +1851,6 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2094,11 +1974,6 @@
       <c r="R10" t="n">
         <v>0.2079289970939578</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2116,12 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2131,11 +2001,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2259,11 +2124,6 @@
       <c r="R11" t="n">
         <v>0.1852600462829624</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2281,12 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2296,11 +2151,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2424,11 +2274,6 @@
       <c r="R12" t="n">
         <v>0.1469573362919701</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2446,12 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2461,11 +2301,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2589,11 +2424,6 @@
       <c r="R13" t="n">
         <v>0.1367953928249722</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2611,12 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2626,11 +2451,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2754,11 +2574,6 @@
       <c r="R14" t="n">
         <v>0.1086546263009779</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2776,12 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2791,11 +2601,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2919,11 +2724,6 @@
       <c r="R15" t="n">
         <v>0.09458424303898079</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -2941,12 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2956,11 +2751,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3084,11 +2874,6 @@
       <c r="R16" t="n">
         <v>0.1242883854809747</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3106,12 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3121,11 +2901,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3249,11 +3024,6 @@
       <c r="R17" t="n">
         <v>0.1039644985469789</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3271,12 +3041,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3286,11 +3051,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3414,11 +3174,6 @@
       <c r="R18" t="n">
         <v>0.02818585380887833</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3436,12 +3191,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3451,11 +3201,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3579,11 +3324,6 @@
       <c r="R19" t="n">
         <v>0.06028640953565642</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3601,12 +3341,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3616,11 +3351,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3744,11 +3474,6 @@
       <c r="R20" t="n">
         <v>0.04775936339837717</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3766,12 +3491,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3781,11 +3501,6 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3909,11 +3624,6 @@
       <c r="R21" t="n">
         <v>0.04697642301479721</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -3931,12 +3641,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3946,11 +3651,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4074,11 +3774,6 @@
       <c r="R22" t="n">
         <v>0.04227878071331749</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4096,12 +3791,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4111,11 +3801,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4239,11 +3924,6 @@
       <c r="R23" t="n">
         <v>0.05245700569985689</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4261,12 +3941,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4276,11 +3951,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4404,11 +4074,6 @@
       <c r="R24" t="n">
         <v>0.03758113841183777</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4426,12 +4091,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4441,11 +4101,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4569,11 +4224,6 @@
       <c r="R25" t="n">
         <v>0.04854230378195711</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4591,12 +4241,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4606,11 +4251,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4734,11 +4374,6 @@
       <c r="R26" t="n">
         <v>0.05715464800133661</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4756,12 +4391,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4771,11 +4401,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4899,11 +4524,6 @@
       <c r="R27" t="n">
         <v>0.05715464800133661</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -4921,12 +4541,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4936,11 +4551,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5064,11 +4674,6 @@
       <c r="R28" t="n">
         <v>0.05480582685059674</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5086,12 +4691,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5101,11 +4701,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5229,11 +4824,6 @@
       <c r="R29" t="n">
         <v>0.05793758838491656</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5251,12 +4841,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5266,11 +4851,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5394,11 +4974,6 @@
       <c r="R30" t="n">
         <v>0.07046463452219581</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5416,12 +4991,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5431,11 +5001,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5559,11 +5124,6 @@
       <c r="R31" t="n">
         <v>0.08455756142663498</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5581,12 +5141,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5596,11 +5151,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5724,11 +5274,6 @@
       <c r="R32" t="n">
         <v>0.1190069383041529</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5746,12 +5291,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5761,11 +5301,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5889,11 +5424,6 @@
       <c r="R33" t="n">
         <v>0.1119604748519333</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -5911,12 +5441,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5926,11 +5451,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6054,11 +5574,6 @@
       <c r="R34" t="n">
         <v>0.151107494030931</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6076,12 +5591,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -6091,11 +5601,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6219,11 +5724,6 @@
       <c r="R35" t="n">
         <v>0.1315339844414322</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6241,12 +5741,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6256,11 +5751,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6384,11 +5874,6 @@
       <c r="R36" t="n">
         <v>0.16911512285327</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6406,12 +5891,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6421,11 +5901,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6549,11 +6024,6 @@
       <c r="R37" t="n">
         <v>0.2779438361708835</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6571,12 +6041,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6586,11 +6051,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6714,11 +6174,6 @@
       <c r="R38" t="n">
         <v>0.3640672783646783</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6736,12 +6191,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6751,11 +6201,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6879,11 +6324,6 @@
       <c r="R39" t="n">
         <v>0.4196560455988551</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -6901,12 +6341,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6916,11 +6351,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -7044,11 +6474,6 @@
       <c r="R40" t="n">
         <v>0.7336151394144164</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7066,12 +6491,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -7081,11 +6501,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7209,11 +6624,6 @@
       <c r="R41" t="n">
         <v>1.0037295717495</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7231,12 +6641,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7246,11 +6651,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7374,11 +6774,6 @@
       <c r="R42" t="n">
         <v>1.546307257570408</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7396,12 +6791,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7411,11 +6801,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7539,11 +6924,6 @@
       <c r="R43" t="n">
         <v>3.088699813222917</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7561,12 +6941,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7576,11 +6951,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7704,11 +7074,6 @@
       <c r="R44" t="n">
         <v>4.391512611499959</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7726,12 +7091,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -7741,11 +7101,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7869,11 +7224,6 @@
       <c r="R45" t="n">
         <v>6.7332872987876</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -7891,12 +7241,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7906,11 +7251,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -8034,11 +7374,6 @@
       <c r="R46" t="n">
         <v>6.990091744601825</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8056,12 +7391,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -8071,11 +7401,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8199,11 +7524,6 @@
       <c r="R47" t="n">
         <v>8.313260992851946</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8221,12 +7541,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8236,11 +7551,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8364,11 +7674,6 @@
       <c r="R48" t="n">
         <v>8.029053633612422</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8386,12 +7691,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8401,11 +7701,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8529,11 +7824,6 @@
       <c r="R49" t="n">
         <v>6.990874684985405</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8551,12 +7841,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -8566,11 +7851,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8694,11 +7974,6 @@
       <c r="R50" t="n">
         <v>4.280335077031606</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8716,12 +7991,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8731,11 +8001,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8859,11 +8124,6 @@
       <c r="R51" t="n">
         <v>3.599959883700626</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -8881,12 +8141,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8896,11 +8151,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -9024,11 +8274,6 @@
       <c r="R52" t="n">
         <v>3.467642958875614</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9046,12 +8291,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -9061,11 +8301,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -9189,11 +8424,6 @@
       <c r="R53" t="n">
         <v>2.841290652011651</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9211,12 +8441,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -9226,11 +8451,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9354,11 +8574,6 @@
       <c r="R54" t="n">
         <v>2.631462629212224</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9376,12 +8591,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -9391,11 +8601,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9519,11 +8724,6 @@
       <c r="R55" t="n">
         <v>1.615206011325444</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9541,12 +8741,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9556,11 +8751,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9684,11 +8874,6 @@
       <c r="R56" t="n">
         <v>0.9872878236943213</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9706,12 +8891,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9721,11 +8901,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9849,11 +9024,6 @@
       <c r="R57" t="n">
         <v>0.808777416238092</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -9871,12 +9041,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -9886,11 +9051,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -10014,11 +9174,6 @@
       <c r="R58" t="n">
         <v>0.6913363587010989</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10036,12 +9191,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -10051,11 +9201,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -10179,11 +9324,6 @@
       <c r="R59" t="n">
         <v>0.4752448128330318</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10201,12 +9341,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -10216,11 +9351,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10344,11 +9474,6 @@
       <c r="R60" t="n">
         <v>0.3585866956796187</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10366,12 +9491,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -10381,11 +9501,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10509,11 +9624,6 @@
       <c r="R61" t="n">
         <v>0.3335326034050602</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10531,12 +9641,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10546,11 +9651,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10674,11 +9774,6 @@
       <c r="R62" t="n">
         <v>0.2403626977590457</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10696,12 +9791,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -10711,11 +9801,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10839,11 +9924,6 @@
       <c r="R63" t="n">
         <v>0.1988668574293082</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -10861,12 +9941,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -10876,11 +9951,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -11004,11 +10074,6 @@
       <c r="R64" t="n">
         <v>0.1628515997846303</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11026,12 +10091,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -11041,11 +10101,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -11169,11 +10224,6 @@
       <c r="R65" t="n">
         <v>0.1401463286608117</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11191,12 +10241,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -11206,11 +10251,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11334,11 +10374,6 @@
       <c r="R66" t="n">
         <v>0.1190069383041529</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11356,12 +10391,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -11371,11 +10401,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -11499,11 +10524,6 @@
       <c r="R67" t="n">
         <v>0.09160402487885456</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11521,12 +10541,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -11536,11 +10551,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11664,11 +10674,6 @@
       <c r="R68" t="n">
         <v>0.08220874027589511</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11686,12 +10691,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -11701,11 +10701,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11829,11 +10824,6 @@
       <c r="R69" t="n">
         <v>0.08142579989231516</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -11851,12 +10841,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -11866,11 +10851,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11994,11 +10974,6 @@
       <c r="R70" t="n">
         <v>0.02588507249795017</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12016,12 +10991,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -12031,11 +11001,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -12159,11 +11124,6 @@
       <c r="R71" t="n">
         <v>0.04706376817809121</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12181,12 +11141,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -12196,11 +11151,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -12324,11 +11274,6 @@
       <c r="R72" t="n">
         <v>0.03765101454247297</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12346,12 +11291,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -12361,11 +11301,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12489,11 +11424,6 @@
       <c r="R73" t="n">
         <v>0.04941695658699578</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12511,12 +11441,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -12526,11 +11451,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -12654,11 +11574,6 @@
       <c r="R74" t="n">
         <v>0.03294463772466385</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12676,12 +11591,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -12691,11 +11601,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12819,11 +11724,6 @@
       <c r="R75" t="n">
         <v>0.03451342999726689</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -12841,12 +11741,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -12856,11 +11751,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12984,11 +11874,6 @@
       <c r="R76" t="n">
         <v>0.03608222226986993</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13006,12 +11891,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -13021,11 +11901,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -13149,11 +12024,6 @@
       <c r="R77" t="n">
         <v>0.03372903386096537</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13171,12 +12041,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -13186,11 +12051,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -13314,11 +12174,6 @@
       <c r="R78" t="n">
         <v>0.04706376817809121</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13336,12 +12191,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -13351,11 +12201,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13479,11 +12324,6 @@
       <c r="R79" t="n">
         <v>0.04235739136028209</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13501,12 +12341,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -13516,11 +12351,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -13644,11 +12474,6 @@
       <c r="R80" t="n">
         <v>0.04784816431439274</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13666,12 +12491,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -13681,11 +12501,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13809,11 +12624,6 @@
       <c r="R81" t="n">
         <v>0.03451342999726689</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13831,12 +12641,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -13846,11 +12651,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13974,11 +12774,6 @@
       <c r="R82" t="n">
         <v>0.06745806772193073</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -13996,12 +12791,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -14011,11 +12801,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -14139,11 +12924,6 @@
       <c r="R83" t="n">
         <v>0.0698112561308353</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14161,12 +12941,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -14176,11 +12951,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -14304,11 +13074,6 @@
       <c r="R84" t="n">
         <v>0.1019714977191976</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14326,12 +13091,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -14341,11 +13101,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -14469,11 +13224,6 @@
       <c r="R85" t="n">
         <v>0.1443288890794797</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14491,12 +13241,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -14506,11 +13251,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14634,11 +13374,6 @@
       <c r="R86" t="n">
         <v>0.2211997104370287</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14656,12 +13391,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -14671,11 +13401,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14799,11 +13524,6 @@
       <c r="R87" t="n">
         <v>0.173351546122636</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14821,12 +13541,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -14836,11 +13551,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14964,11 +13674,6 @@
       <c r="R88" t="n">
         <v>0.1874706765760633</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -14986,12 +13691,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -15001,11 +13701,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -15129,11 +13824,6 @@
       <c r="R89" t="n">
         <v>0.425142705875424</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15151,12 +13841,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -15166,11 +13851,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -15294,11 +13974,6 @@
       <c r="R90" t="n">
         <v>0.6165353631329948</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15316,12 +13991,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -15331,11 +14001,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -15459,11 +14124,6 @@
       <c r="R91" t="n">
         <v>0.8918584069748285</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15481,12 +14141,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -15496,11 +14151,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15624,11 +14274,6 @@
       <c r="R92" t="n">
         <v>1.196204107859818</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15646,12 +14291,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -15661,11 +14301,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -15789,11 +14424,6 @@
       <c r="R93" t="n">
         <v>2.109241210514788</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15811,12 +14441,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -15826,11 +14451,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -15954,11 +14574,6 @@
       <c r="R94" t="n">
         <v>3.235634062243771</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -15976,12 +14591,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -15991,11 +14601,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -16119,11 +14724,6 @@
       <c r="R95" t="n">
         <v>4.29770643079603</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16141,12 +14741,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -16156,11 +14751,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -16284,11 +14874,6 @@
       <c r="R96" t="n">
         <v>6.283013051775177</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16306,12 +14891,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -16321,11 +14901,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16449,11 +15024,6 @@
       <c r="R97" t="n">
         <v>9.222929770633275</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16471,12 +15041,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -16486,11 +15051,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -16614,11 +15174,6 @@
       <c r="R98" t="n">
         <v>12.19500673107973</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16636,12 +15191,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -16651,11 +15201,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -16779,11 +15324,6 @@
       <c r="R99" t="n">
         <v>10.18067745305743</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16801,12 +15341,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -16816,11 +15351,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -16944,11 +15474,6 @@
       <c r="R100" t="n">
         <v>10.85447373414044</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -16966,12 +15491,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -16981,11 +15501,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -17109,11 +15624,6 @@
       <c r="R101" t="n">
         <v>9.00878962542296</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17131,12 +15641,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -17146,11 +15651,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -17274,11 +15774,6 @@
       <c r="R102" t="n">
         <v>5.716679041365479</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17296,12 +15791,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -17311,11 +15801,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17439,11 +15924,6 @@
       <c r="R103" t="n">
         <v>5.507245272972973</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17461,12 +15941,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -17476,11 +15951,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -17604,11 +16074,6 @@
       <c r="R104" t="n">
         <v>5.552740248878462</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17626,12 +16091,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -17641,11 +16101,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -17769,11 +16224,6 @@
       <c r="R105" t="n">
         <v>4.904044644157104</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17791,12 +16241,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -17806,11 +16251,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -17934,11 +16374,6 @@
       <c r="R106" t="n">
         <v>4.147886768762438</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -17956,12 +16391,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -17971,11 +16401,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -18099,11 +16524,6 @@
       <c r="R107" t="n">
         <v>2.2700424184566</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18121,12 +16541,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -18136,11 +16551,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -18264,11 +16674,6 @@
       <c r="R108" t="n">
         <v>1.549966765331804</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18286,12 +16691,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -18301,11 +16701,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -18429,11 +16824,6 @@
       <c r="R109" t="n">
         <v>1.236992706947498</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18451,12 +16841,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -18466,11 +16851,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -18594,11 +16974,6 @@
       <c r="R110" t="n">
         <v>0.9240186485631908</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18616,12 +16991,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -18631,11 +17001,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -18759,11 +17124,6 @@
       <c r="R111" t="n">
         <v>0.559274445182984</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18781,12 +17141,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -18796,11 +17151,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -18924,11 +17274,6 @@
       <c r="R112" t="n">
         <v>0.4376930440562483</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -18946,12 +17291,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -18961,11 +17301,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -19089,11 +17424,6 @@
       <c r="R113" t="n">
         <v>0.4188675367850118</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19111,12 +17441,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -19126,11 +17451,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -19254,11 +17574,6 @@
       <c r="R114" t="n">
         <v>0.310620869975402</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19276,12 +17591,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -19291,11 +17601,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -19419,11 +17724,6 @@
       <c r="R115" t="n">
         <v>0.2651258940699138</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19441,12 +17741,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -19456,11 +17751,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -19584,11 +17874,6 @@
       <c r="R116" t="n">
         <v>0.2290436718000439</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19606,12 +17891,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -19621,11 +17901,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -19749,11 +18024,6 @@
       <c r="R117" t="n">
         <v>0.1921770533938724</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19771,12 +18041,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -19786,11 +18051,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -19914,11 +18174,6 @@
       <c r="R118" t="n">
         <v>0.2251216911185363</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -19936,12 +18191,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -19951,11 +18201,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -20079,11 +18324,6 @@
       <c r="R119" t="n">
         <v>0.1639387924870177</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -20101,12 +18341,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -20116,11 +18351,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -20244,11 +18474,6 @@
       <c r="R120" t="n">
         <v>0.1419757006705752</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -20266,12 +18491,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -20281,11 +18501,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -20409,11 +18624,6 @@
       <c r="R121" t="n">
         <v>0.1192282127178311</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_fe2cf00297cb0527346dbfb1d14b</t>
@@ -20431,12 +18641,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -20446,11 +18651,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
